--- a/DataTables/DetailText/剧情/000_03如何出书.xlsx
+++ b/DataTables/DetailText/剧情/000_03如何出书.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8384E52-80F0-43CD-8FD6-301EB32BD46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93FCC35-CCBE-4F1A-A576-C23F010BEC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20490" yWindow="4500" windowWidth="20490" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>LineIndex</t>
   </si>
@@ -247,6 +247,10 @@
   </si>
   <si>
     <t>000_03</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -394,7 +398,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -479,6 +483,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1047,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -1061,7 +1074,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1086,8 +1099,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1108,8 +1124,9 @@
       <c r="H2" s="27" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="31"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1130,8 +1147,9 @@
       <c r="H3" s="27" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="31"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1150,8 +1168,9 @@
       <c r="H4" s="27" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="31"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1172,8 +1191,9 @@
       <c r="H5" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="31"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1192,8 +1212,9 @@
       <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="31"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1214,8 +1235,9 @@
       <c r="H7" s="29" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1236,8 +1258,9 @@
       <c r="H8" s="29" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1258,8 +1281,9 @@
       <c r="H9" s="29" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1280,8 +1304,9 @@
       <c r="H10" s="29" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1300,8 +1325,9 @@
       <c r="H11" s="29" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3"/>
@@ -1310,8 +1336,9 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="32"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3"/>
@@ -1320,8 +1347,9 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1330,8 +1358,9 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="32"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1340,8 +1369,9 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1350,8 +1380,9 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="32"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1360,6 +1391,7 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
+      <c r="I17" s="32"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/DataTables/DetailText/剧情/000_03如何出书.xlsx
+++ b/DataTables/DetailText/剧情/000_03如何出书.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93FCC35-CCBE-4F1A-A576-C23F010BEC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6EFC8A6-D4FB-4F57-AEEA-E64E3F98BB29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20490" yWindow="4500" windowWidth="20490" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -174,10 +174,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>爹，今天和书商谈的怎么样？</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>李东璧</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -251,6 +247,10 @@
   </si>
   <si>
     <t>Music</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>爹，今天和书商谈得怎么样？</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -789,7 +789,7 @@
     </row>
     <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>32</v>
@@ -806,7 +806,7 @@
       <c r="H2" s="23"/>
       <c r="I2" s="22"/>
       <c r="J2" s="25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K2" s="23"/>
       <c r="L2" s="23" t="s">
@@ -1100,7 +1100,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1122,7 +1122,7 @@
         <v>10</v>
       </c>
       <c r="H2" s="27" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I2" s="31"/>
     </row>
@@ -1134,18 +1134,18 @@
         <v>9</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="2"/>
       <c r="H3" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" s="31"/>
     </row>
@@ -1166,7 +1166,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="2"/>
       <c r="H4" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I4" s="31"/>
     </row>
@@ -1178,18 +1178,18 @@
         <v>9</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I5" s="31"/>
     </row>
@@ -1210,7 +1210,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I6" s="31"/>
     </row>
@@ -1222,18 +1222,18 @@
         <v>9</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I7" s="32"/>
     </row>
@@ -1245,18 +1245,18 @@
         <v>9</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I8" s="32"/>
     </row>
@@ -1268,18 +1268,18 @@
         <v>9</v>
       </c>
       <c r="C9" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="28" t="s">
-        <v>45</v>
-      </c>
       <c r="E9" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I9" s="32"/>
     </row>
@@ -1291,18 +1291,18 @@
         <v>9</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I10" s="32"/>
     </row>
@@ -1323,7 +1323,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I11" s="32"/>
     </row>
